--- a/data/raw_data/DOC/ROTUI_NPOC_TN_241108.xlsx
+++ b/data/raw_data/DOC/ROTUI_NPOC_TN_241108.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keanurochette/Desktop/Git Hub Repository/MOBEAST/data/raw_data/DOC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FB3DD30-A735-6A4D-BD04-5459C3A8DBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DAB9FC-C7E1-3E4F-B629-195131EADC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16800" xr2:uid="{879BD7D6-514C-F446-9689-B4F1014DCB9C}"/>
+    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16800" activeTab="1" xr2:uid="{879BD7D6-514C-F446-9689-B4F1014DCB9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="357">
   <si>
     <t>TAU824001</t>
   </si>
@@ -264,6 +265,849 @@
   </si>
   <si>
     <t>TN (uM)</t>
+  </si>
+  <si>
+    <t>0.55238</t>
+  </si>
+  <si>
+    <t>0.113721428571429</t>
+  </si>
+  <si>
+    <t>45.9906583296561</t>
+  </si>
+  <si>
+    <t>8.11907362700911</t>
+  </si>
+  <si>
+    <t>0.84268</t>
+  </si>
+  <si>
+    <t>0.128111428571429</t>
+  </si>
+  <si>
+    <t>70.1607733104648</t>
+  </si>
+  <si>
+    <t>9.14643910210318</t>
+  </si>
+  <si>
+    <t>0.81288</t>
+  </si>
+  <si>
+    <t>0.118951428571429</t>
+  </si>
+  <si>
+    <t>67.6796523100236</t>
+  </si>
+  <si>
+    <t>8.49246636048666</t>
+  </si>
+  <si>
+    <t>0.80188</t>
+  </si>
+  <si>
+    <t>0.122221428571429</t>
+  </si>
+  <si>
+    <t>66.7638022763036</t>
+  </si>
+  <si>
+    <t>8.72592606191527</t>
+  </si>
+  <si>
+    <t>0.81518</t>
+  </si>
+  <si>
+    <t>0.114671428571429</t>
+  </si>
+  <si>
+    <t>67.871148226165</t>
+  </si>
+  <si>
+    <t>8.18689831091039</t>
+  </si>
+  <si>
+    <t>0.88138</t>
+  </si>
+  <si>
+    <t>0.152951428571429</t>
+  </si>
+  <si>
+    <t>73.3829002472795</t>
+  </si>
+  <si>
+    <t>10.9198761001113</t>
+  </si>
+  <si>
+    <t>1.45788</t>
+  </si>
+  <si>
+    <t>0.136081428571429</t>
+  </si>
+  <si>
+    <t>121.381767923601</t>
+  </si>
+  <si>
+    <t>9.71545250283283</t>
+  </si>
+  <si>
+    <t>0.85648</t>
+  </si>
+  <si>
+    <t>0.139151428571429</t>
+  </si>
+  <si>
+    <t>71.3097488073135</t>
+  </si>
+  <si>
+    <t>9.93463332344011</t>
+  </si>
+  <si>
+    <t>0.84448</t>
+  </si>
+  <si>
+    <t>0.142041428571429</t>
+  </si>
+  <si>
+    <t>70.310639679619</t>
+  </si>
+  <si>
+    <t>10.1409631513082</t>
+  </si>
+  <si>
+    <t>0.85078</t>
+  </si>
+  <si>
+    <t>0.122741428571429</t>
+  </si>
+  <si>
+    <t>70.8351719716586</t>
+  </si>
+  <si>
+    <t>8.7630511520507</t>
+  </si>
+  <si>
+    <t>0.86518</t>
+  </si>
+  <si>
+    <t>0.116791428571429</t>
+  </si>
+  <si>
+    <t>72.034102924892</t>
+  </si>
+  <si>
+    <t>8.33825444761639</t>
+  </si>
+  <si>
+    <t>0.78298</t>
+  </si>
+  <si>
+    <t>0.140681428571429</t>
+  </si>
+  <si>
+    <t>65.1902054001849</t>
+  </si>
+  <si>
+    <t>10.0438667617232</t>
+  </si>
+  <si>
+    <t>0.83248</t>
+  </si>
+  <si>
+    <t>0.140511428571429</t>
+  </si>
+  <si>
+    <t>69.3115305519245</t>
+  </si>
+  <si>
+    <t>10.0317297130251</t>
+  </si>
+  <si>
+    <t>0.84388</t>
+  </si>
+  <si>
+    <t>0.145281428571429</t>
+  </si>
+  <si>
+    <t>70.2606842232343</t>
+  </si>
+  <si>
+    <t>10.3722810206136</t>
+  </si>
+  <si>
+    <t>0.79598</t>
+  </si>
+  <si>
+    <t>0.121591428571429</t>
+  </si>
+  <si>
+    <t>66.2725736218539</t>
+  </si>
+  <si>
+    <t>8.68094758732811</t>
+  </si>
+  <si>
+    <t>0.86818</t>
+  </si>
+  <si>
+    <t>0.128811428571429</t>
+  </si>
+  <si>
+    <t>72.2838802068156</t>
+  </si>
+  <si>
+    <t>9.1964151849778</t>
+  </si>
+  <si>
+    <t>1.09488</t>
+  </si>
+  <si>
+    <t>0.134221428571429</t>
+  </si>
+  <si>
+    <t>91.1587168108437</t>
+  </si>
+  <si>
+    <t>9.58265891119454</t>
+  </si>
+  <si>
+    <t>0.78638</t>
+  </si>
+  <si>
+    <t>0.144861428571429</t>
+  </si>
+  <si>
+    <t>65.4732863196983</t>
+  </si>
+  <si>
+    <t>10.3422953708888</t>
+  </si>
+  <si>
+    <t>0.54688</t>
+  </si>
+  <si>
+    <t>0.108181428571429</t>
+  </si>
+  <si>
+    <t>45.5327333127961</t>
+  </si>
+  <si>
+    <t>7.72354862825852</t>
+  </si>
+  <si>
+    <t>0.81208</t>
+  </si>
+  <si>
+    <t>0.130281428571429</t>
+  </si>
+  <si>
+    <t>67.6130450348439</t>
+  </si>
+  <si>
+    <t>9.30136495901451</t>
+  </si>
+  <si>
+    <t>0.91468</t>
+  </si>
+  <si>
+    <t>0.135411428571429</t>
+  </si>
+  <si>
+    <t>76.1554280766317</t>
+  </si>
+  <si>
+    <t>9.6676182520814</t>
+  </si>
+  <si>
+    <t>0.84928</t>
+  </si>
+  <si>
+    <t>0.130781428571429</t>
+  </si>
+  <si>
+    <t>70.7102833306968</t>
+  </si>
+  <si>
+    <t>9.33706216106781</t>
+  </si>
+  <si>
+    <t>0.79728</t>
+  </si>
+  <si>
+    <t>0.136311428571429</t>
+  </si>
+  <si>
+    <t>66.3808104440208</t>
+  </si>
+  <si>
+    <t>9.73187321577735</t>
+  </si>
+  <si>
+    <t>0.76988</t>
+  </si>
+  <si>
+    <t>0.126771428571429</t>
+  </si>
+  <si>
+    <t>64.0995112691184</t>
+  </si>
+  <si>
+    <t>9.05077060060033</t>
+  </si>
+  <si>
+    <t>0.83638</t>
+  </si>
+  <si>
+    <t>0.113431428571429</t>
+  </si>
+  <si>
+    <t>69.6362410184253</t>
+  </si>
+  <si>
+    <t>8.0983692498182</t>
+  </si>
+  <si>
+    <t>0.85018</t>
+  </si>
+  <si>
+    <t>0.135551428571429</t>
+  </si>
+  <si>
+    <t>70.7852165152739</t>
+  </si>
+  <si>
+    <t>9.67761346865633</t>
+  </si>
+  <si>
+    <t>0.80258</t>
+  </si>
+  <si>
+    <t>0.118021428571429</t>
+  </si>
+  <si>
+    <t>66.8220836420858</t>
+  </si>
+  <si>
+    <t>8.42606956466752</t>
+  </si>
+  <si>
+    <t>0.95718</t>
+  </si>
+  <si>
+    <t>0.139451428571429</t>
+  </si>
+  <si>
+    <t>79.6939395705496</t>
+  </si>
+  <si>
+    <t>9.95605164467209</t>
+  </si>
+  <si>
+    <t>0.78598</t>
+  </si>
+  <si>
+    <t>0.135471428571429</t>
+  </si>
+  <si>
+    <t>65.4399826821085</t>
+  </si>
+  <si>
+    <t>9.6719019163278</t>
+  </si>
+  <si>
+    <t>0.84958</t>
+  </si>
+  <si>
+    <t>0.139891428571429</t>
+  </si>
+  <si>
+    <t>70.7352610588892</t>
+  </si>
+  <si>
+    <t>9.987465182479</t>
+  </si>
+  <si>
+    <t>0.77588</t>
+  </si>
+  <si>
+    <t>0.137511428571429</t>
+  </si>
+  <si>
+    <t>64.5990658329656</t>
+  </si>
+  <si>
+    <t>9.81754650070527</t>
+  </si>
+  <si>
+    <t>0.74158</t>
+  </si>
+  <si>
+    <t>0.117311428571429</t>
+  </si>
+  <si>
+    <t>61.7432789096389</t>
+  </si>
+  <si>
+    <t>8.37537953775183</t>
+  </si>
+  <si>
+    <t>0.78148</t>
+  </si>
+  <si>
+    <t>0.120711428571429</t>
+  </si>
+  <si>
+    <t>65.065316759223</t>
+  </si>
+  <si>
+    <t>8.61812051171429</t>
+  </si>
+  <si>
+    <t>0.71988</t>
+  </si>
+  <si>
+    <t>0.129531428571429</t>
+  </si>
+  <si>
+    <t>59.9365565703914</t>
+  </si>
+  <si>
+    <t>9.24781915593456</t>
+  </si>
+  <si>
+    <t>0.75718</t>
+  </si>
+  <si>
+    <t>0.121941428571429</t>
+  </si>
+  <si>
+    <t>63.0421207756417</t>
+  </si>
+  <si>
+    <t>8.70593562876542</t>
+  </si>
+  <si>
+    <t>0.154661428571429</t>
+  </si>
+  <si>
+    <t>11.0419605311336</t>
+  </si>
+  <si>
+    <t>0.47198</t>
+  </si>
+  <si>
+    <t>0.0993914285714286</t>
+  </si>
+  <si>
+    <t>39.2966271741031</t>
+  </si>
+  <si>
+    <t>7.09599181616145</t>
+  </si>
+  <si>
+    <t>0.79458</t>
+  </si>
+  <si>
+    <t>0.153721428571429</t>
+  </si>
+  <si>
+    <t>66.1560108902895</t>
+  </si>
+  <si>
+    <t>10.9748497912734</t>
+  </si>
+  <si>
+    <t>0.81888</t>
+  </si>
+  <si>
+    <t>0.150661428571429</t>
+  </si>
+  <si>
+    <t>68.1792068738708</t>
+  </si>
+  <si>
+    <t>10.7563829147071</t>
+  </si>
+  <si>
+    <t>0.83338</t>
+  </si>
+  <si>
+    <t>0.134401428571429</t>
+  </si>
+  <si>
+    <t>69.3864637365016</t>
+  </si>
+  <si>
+    <t>9.59550990393373</t>
+  </si>
+  <si>
+    <t>0.78928</t>
+  </si>
+  <si>
+    <t>0.132721428571429</t>
+  </si>
+  <si>
+    <t>65.7147376922244</t>
+  </si>
+  <si>
+    <t>9.47556730503463</t>
+  </si>
+  <si>
+    <t>0.85408</t>
+  </si>
+  <si>
+    <t>0.125741428571429</t>
+  </si>
+  <si>
+    <t>71.1099269817746</t>
+  </si>
+  <si>
+    <t>8.97723436437052</t>
+  </si>
+  <si>
+    <t>0.79538</t>
+  </si>
+  <si>
+    <t>0.123261428571429</t>
+  </si>
+  <si>
+    <t>66.2226181654691</t>
+  </si>
+  <si>
+    <t>8.80017624218614</t>
+  </si>
+  <si>
+    <t>0.85228</t>
+  </si>
+  <si>
+    <t>0.132631428571429</t>
+  </si>
+  <si>
+    <t>70.9600606126204</t>
+  </si>
+  <si>
+    <t>9.46914180866504</t>
+  </si>
+  <si>
+    <t>0.121901428571429</t>
+  </si>
+  <si>
+    <t>8.70307985260115</t>
+  </si>
+  <si>
+    <t>0.77428</t>
+  </si>
+  <si>
+    <t>0.132851428571429</t>
+  </si>
+  <si>
+    <t>64.4658512826064</t>
+  </si>
+  <si>
+    <t>9.48484857756849</t>
+  </si>
+  <si>
+    <t>0.79168</t>
+  </si>
+  <si>
+    <t>0.123431428571429</t>
+  </si>
+  <si>
+    <t>65.9145595177633</t>
+  </si>
+  <si>
+    <t>8.81231329088426</t>
+  </si>
+  <si>
+    <t>0.68158</t>
+  </si>
+  <si>
+    <t>0.127791428571429</t>
+  </si>
+  <si>
+    <t>56.7477332711666</t>
+  </si>
+  <si>
+    <t>9.12359289278906</t>
+  </si>
+  <si>
+    <t>0.78748</t>
+  </si>
+  <si>
+    <t>0.132331428571429</t>
+  </si>
+  <si>
+    <t>65.5648713230703</t>
+  </si>
+  <si>
+    <t>9.44772348743306</t>
+  </si>
+  <si>
+    <t>0.72608</t>
+  </si>
+  <si>
+    <t>0.114591428571429</t>
+  </si>
+  <si>
+    <t>60.4527629530335</t>
+  </si>
+  <si>
+    <t>8.18118675858186</t>
+  </si>
+  <si>
+    <t>0.80518</t>
+  </si>
+  <si>
+    <t>0.132811428571429</t>
+  </si>
+  <si>
+    <t>67.0385572864196</t>
+  </si>
+  <si>
+    <t>9.48199280140423</t>
+  </si>
+  <si>
+    <t>0.81448</t>
+  </si>
+  <si>
+    <t>0.130201428571429</t>
+  </si>
+  <si>
+    <t>67.8128668603828</t>
+  </si>
+  <si>
+    <t>9.29565340668598</t>
+  </si>
+  <si>
+    <t>0.74768</t>
+  </si>
+  <si>
+    <t>0.117951428571429</t>
+  </si>
+  <si>
+    <t>62.2511593828836</t>
+  </si>
+  <si>
+    <t>8.42107195638006</t>
+  </si>
+  <si>
+    <t>0.64748</t>
+  </si>
+  <si>
+    <t>0.118631428571429</t>
+  </si>
+  <si>
+    <t>53.9085981666348</t>
+  </si>
+  <si>
+    <t>8.46962015117255</t>
+  </si>
+  <si>
+    <t>0.42828</t>
+  </si>
+  <si>
+    <t>0.0969614285714286</t>
+  </si>
+  <si>
+    <t>35.6582047674157</t>
+  </si>
+  <si>
+    <t>6.9225034141824</t>
+  </si>
+  <si>
+    <t>0.77778</t>
+  </si>
+  <si>
+    <t>0.126041428571429</t>
+  </si>
+  <si>
+    <t>64.7572581115172</t>
+  </si>
+  <si>
+    <t>8.9986526856025</t>
+  </si>
+  <si>
+    <t>0.84688</t>
+  </si>
+  <si>
+    <t>0.137381428571429</t>
+  </si>
+  <si>
+    <t>70.5104615051579</t>
+  </si>
+  <si>
+    <t>9.80826522817142</t>
+  </si>
+  <si>
+    <t>0.80388</t>
+  </si>
+  <si>
+    <t>0.135781428571429</t>
+  </si>
+  <si>
+    <t>66.9303204642527</t>
+  </si>
+  <si>
+    <t>9.69403418160084</t>
+  </si>
+  <si>
+    <t>0.82128</t>
+  </si>
+  <si>
+    <t>0.127401428571429</t>
+  </si>
+  <si>
+    <t>68.3790286994097</t>
+  </si>
+  <si>
+    <t>9.09574907518748</t>
+  </si>
+  <si>
+    <t>0.70068</t>
+  </si>
+  <si>
+    <t>0.119991428571429</t>
+  </si>
+  <si>
+    <t>58.3379819660803</t>
+  </si>
+  <si>
+    <t>8.56671654075753</t>
+  </si>
+  <si>
+    <t>0.817683333333333</t>
+  </si>
+  <si>
+    <t>0.146133333333333</t>
+  </si>
+  <si>
+    <t>68.0795734914146</t>
+  </si>
+  <si>
+    <t>10.4331022534454</t>
+  </si>
+  <si>
+    <t>0.758783333333333</t>
+  </si>
+  <si>
+    <t>0.128923333333333</t>
+  </si>
+  <si>
+    <t>63.1756128563142</t>
+  </si>
+  <si>
+    <t>9.20440455877069</t>
+  </si>
+  <si>
+    <t>0.535383333333333</t>
+  </si>
+  <si>
+    <t>0.124263333333333</t>
+  </si>
+  <si>
+    <t>44.5755312624021</t>
+  </si>
+  <si>
+    <t>8.8717066356339</t>
+  </si>
+  <si>
+    <t>0.334983333333333</t>
+  </si>
+  <si>
+    <t>0.109433333333333</t>
+  </si>
+  <si>
+    <t>27.8904088299044</t>
+  </si>
+  <si>
+    <t>7.81292762273293</t>
+  </si>
+  <si>
+    <t>0.818983333333333</t>
+  </si>
+  <si>
+    <t>0.141133333333333</t>
+  </si>
+  <si>
+    <t>68.1878103135815</t>
+  </si>
+  <si>
+    <t>10.0761302329123</t>
+  </si>
+  <si>
+    <t>0.761183333333333</t>
+  </si>
+  <si>
+    <t>0.130283333333333</t>
+  </si>
+  <si>
+    <t>63.3754346818531</t>
+  </si>
+  <si>
+    <t>9.30150094835567</t>
+  </si>
+  <si>
+    <t>0.789483333333333</t>
+  </si>
+  <si>
+    <t>0.135743333333333</t>
+  </si>
+  <si>
+    <t>65.7316670413326</t>
+  </si>
+  <si>
+    <t>9.69131439477774</t>
+  </si>
+  <si>
+    <t>0.766783333333333</t>
+  </si>
+  <si>
+    <t>0.132943333333333</t>
+  </si>
+  <si>
+    <t>63.8416856081105</t>
+  </si>
+  <si>
+    <t>9.49141006327924</t>
+  </si>
+  <si>
+    <t>0.827283333333333</t>
+  </si>
+  <si>
+    <t>0.145793333333333</t>
+  </si>
+  <si>
+    <t>68.8788607935702</t>
+  </si>
+  <si>
+    <t>10.4088281560491</t>
+  </si>
+  <si>
+    <t>0.778983333333333</t>
+  </si>
+  <si>
+    <t>0.147343333333333</t>
+  </si>
+  <si>
+    <t>64.8574465545999</t>
+  </si>
+  <si>
+    <t>10.5194894824144</t>
+  </si>
+  <si>
+    <t>1.80488333333333</t>
+  </si>
+  <si>
+    <t>2.98403333333333</t>
+  </si>
+  <si>
+    <t>150.27295106308</t>
+  </si>
+  <si>
+    <t>213.043281667583</t>
+  </si>
+  <si>
+    <t>Sample ID</t>
   </si>
 </sst>
 </file>
@@ -1868,4 +2712,1238 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32052E23-2198-864F-B6D5-C6FEBFD2D5DA}">
+  <dimension ref="A1:E72"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" t="s">
+        <v>150</v>
+      </c>
+      <c r="E20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" t="s">
+        <v>169</v>
+      </c>
+      <c r="D25" t="s">
+        <v>170</v>
+      </c>
+      <c r="E25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" t="s">
+        <v>181</v>
+      </c>
+      <c r="D28" t="s">
+        <v>182</v>
+      </c>
+      <c r="E28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" t="s">
+        <v>185</v>
+      </c>
+      <c r="D29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" t="s">
+        <v>190</v>
+      </c>
+      <c r="E30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>200</v>
+      </c>
+      <c r="C33" t="s">
+        <v>201</v>
+      </c>
+      <c r="D33" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>204</v>
+      </c>
+      <c r="C34" t="s">
+        <v>205</v>
+      </c>
+      <c r="D34" t="s">
+        <v>206</v>
+      </c>
+      <c r="E34" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>212</v>
+      </c>
+      <c r="C36" t="s">
+        <v>213</v>
+      </c>
+      <c r="D36" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" t="s">
+        <v>220</v>
+      </c>
+      <c r="E38" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>222</v>
+      </c>
+      <c r="C39" t="s">
+        <v>223</v>
+      </c>
+      <c r="D39" t="s">
+        <v>224</v>
+      </c>
+      <c r="E39" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>226</v>
+      </c>
+      <c r="C40" t="s">
+        <v>227</v>
+      </c>
+      <c r="D40" t="s">
+        <v>228</v>
+      </c>
+      <c r="E40" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>230</v>
+      </c>
+      <c r="C41" t="s">
+        <v>231</v>
+      </c>
+      <c r="D41" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>234</v>
+      </c>
+      <c r="C42" t="s">
+        <v>235</v>
+      </c>
+      <c r="D42" t="s">
+        <v>236</v>
+      </c>
+      <c r="E42" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>238</v>
+      </c>
+      <c r="C43" t="s">
+        <v>239</v>
+      </c>
+      <c r="D43" t="s">
+        <v>240</v>
+      </c>
+      <c r="E43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>242</v>
+      </c>
+      <c r="C44" t="s">
+        <v>243</v>
+      </c>
+      <c r="D44" t="s">
+        <v>244</v>
+      </c>
+      <c r="E44" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>246</v>
+      </c>
+      <c r="C45" t="s">
+        <v>247</v>
+      </c>
+      <c r="D45" t="s">
+        <v>248</v>
+      </c>
+      <c r="E45" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>234</v>
+      </c>
+      <c r="C46" t="s">
+        <v>250</v>
+      </c>
+      <c r="D46" t="s">
+        <v>236</v>
+      </c>
+      <c r="E46" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>252</v>
+      </c>
+      <c r="C47" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" t="s">
+        <v>254</v>
+      </c>
+      <c r="E47" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>256</v>
+      </c>
+      <c r="C48" t="s">
+        <v>257</v>
+      </c>
+      <c r="D48" t="s">
+        <v>258</v>
+      </c>
+      <c r="E48" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>260</v>
+      </c>
+      <c r="C49" t="s">
+        <v>261</v>
+      </c>
+      <c r="D49" t="s">
+        <v>262</v>
+      </c>
+      <c r="E49" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>264</v>
+      </c>
+      <c r="C50" t="s">
+        <v>265</v>
+      </c>
+      <c r="D50" t="s">
+        <v>266</v>
+      </c>
+      <c r="E50" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>268</v>
+      </c>
+      <c r="C51" t="s">
+        <v>269</v>
+      </c>
+      <c r="D51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E51" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>272</v>
+      </c>
+      <c r="C52" t="s">
+        <v>273</v>
+      </c>
+      <c r="D52" t="s">
+        <v>274</v>
+      </c>
+      <c r="E52" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>276</v>
+      </c>
+      <c r="C53" t="s">
+        <v>277</v>
+      </c>
+      <c r="D53" t="s">
+        <v>278</v>
+      </c>
+      <c r="E53" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>280</v>
+      </c>
+      <c r="C54" t="s">
+        <v>281</v>
+      </c>
+      <c r="D54" t="s">
+        <v>282</v>
+      </c>
+      <c r="E54" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>284</v>
+      </c>
+      <c r="C55" t="s">
+        <v>285</v>
+      </c>
+      <c r="D55" t="s">
+        <v>286</v>
+      </c>
+      <c r="E55" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>288</v>
+      </c>
+      <c r="C56" t="s">
+        <v>289</v>
+      </c>
+      <c r="D56" t="s">
+        <v>290</v>
+      </c>
+      <c r="E56" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>292</v>
+      </c>
+      <c r="C57" t="s">
+        <v>293</v>
+      </c>
+      <c r="D57" t="s">
+        <v>294</v>
+      </c>
+      <c r="E57" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>296</v>
+      </c>
+      <c r="C58" t="s">
+        <v>297</v>
+      </c>
+      <c r="D58" t="s">
+        <v>298</v>
+      </c>
+      <c r="E58" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>300</v>
+      </c>
+      <c r="C59" t="s">
+        <v>301</v>
+      </c>
+      <c r="D59" t="s">
+        <v>302</v>
+      </c>
+      <c r="E59" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>304</v>
+      </c>
+      <c r="C60" t="s">
+        <v>305</v>
+      </c>
+      <c r="D60" t="s">
+        <v>306</v>
+      </c>
+      <c r="E60" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>308</v>
+      </c>
+      <c r="C61" t="s">
+        <v>309</v>
+      </c>
+      <c r="D61" t="s">
+        <v>310</v>
+      </c>
+      <c r="E61" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>312</v>
+      </c>
+      <c r="C62" t="s">
+        <v>313</v>
+      </c>
+      <c r="D62" t="s">
+        <v>314</v>
+      </c>
+      <c r="E62" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>316</v>
+      </c>
+      <c r="C63" t="s">
+        <v>317</v>
+      </c>
+      <c r="D63" t="s">
+        <v>318</v>
+      </c>
+      <c r="E63" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>320</v>
+      </c>
+      <c r="C64" t="s">
+        <v>321</v>
+      </c>
+      <c r="D64" t="s">
+        <v>322</v>
+      </c>
+      <c r="E64" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>324</v>
+      </c>
+      <c r="C65" t="s">
+        <v>325</v>
+      </c>
+      <c r="D65" t="s">
+        <v>326</v>
+      </c>
+      <c r="E65" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>328</v>
+      </c>
+      <c r="C66" t="s">
+        <v>329</v>
+      </c>
+      <c r="D66" t="s">
+        <v>330</v>
+      </c>
+      <c r="E66" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>332</v>
+      </c>
+      <c r="C67" t="s">
+        <v>333</v>
+      </c>
+      <c r="D67" t="s">
+        <v>334</v>
+      </c>
+      <c r="E67" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>336</v>
+      </c>
+      <c r="C68" t="s">
+        <v>337</v>
+      </c>
+      <c r="D68" t="s">
+        <v>338</v>
+      </c>
+      <c r="E68" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>340</v>
+      </c>
+      <c r="C69" t="s">
+        <v>341</v>
+      </c>
+      <c r="D69" t="s">
+        <v>342</v>
+      </c>
+      <c r="E69" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>344</v>
+      </c>
+      <c r="C70" t="s">
+        <v>345</v>
+      </c>
+      <c r="D70" t="s">
+        <v>346</v>
+      </c>
+      <c r="E70" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>348</v>
+      </c>
+      <c r="C71" t="s">
+        <v>349</v>
+      </c>
+      <c r="D71" t="s">
+        <v>350</v>
+      </c>
+      <c r="E71" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>352</v>
+      </c>
+      <c r="C72" t="s">
+        <v>353</v>
+      </c>
+      <c r="D72" t="s">
+        <v>354</v>
+      </c>
+      <c r="E72" t="s">
+        <v>355</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>